--- a/Data/Salidas/Salidas_consolidado correcciones.xlsx
+++ b/Data/Salidas/Salidas_consolidado correcciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SupplyDestileria\Documents\Bosque\Claude\Tablero operativo\Data\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A228A14-3F44-4548-9E0B-3FF00D0EF5C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629F5DE0-CC78-40B7-9C17-6092EEF49DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Correcciones" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Correcciones!$A$1:$F$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Correcciones!$A$1:$G$32</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="33">
   <si>
     <t>FECHA</t>
   </si>
@@ -74,6 +74,54 @@
   </si>
   <si>
     <t>110040</t>
+  </si>
+  <si>
+    <t>LOS TEMPLOS CABALLITO S.R.L.</t>
+  </si>
+  <si>
+    <t>900007</t>
+  </si>
+  <si>
+    <t>TEMPLE BARRIO CHINO</t>
+  </si>
+  <si>
+    <t>TEMPLE MONROE</t>
+  </si>
+  <si>
+    <t>GC_REMITO</t>
+  </si>
+  <si>
+    <t>900008</t>
+  </si>
+  <si>
+    <t>OSTERIA FANTASTICO</t>
+  </si>
+  <si>
+    <t>OFICINA</t>
+  </si>
+  <si>
+    <t>GREEN UMBRELLA PRODUCCIONES SAS</t>
+  </si>
+  <si>
+    <t>CULTURAL VIVO</t>
+  </si>
+  <si>
+    <t>BOSQUE_SALIDAS</t>
+  </si>
+  <si>
+    <t>900003</t>
+  </si>
+  <si>
+    <t>KSENIIA ROMANTSOVA</t>
+  </si>
+  <si>
+    <t>KLOZER_MKT</t>
+  </si>
+  <si>
+    <t>MUSGO</t>
+  </si>
+  <si>
+    <t>ENVIOS INTERNACIONALES</t>
   </si>
 </sst>
 </file>
@@ -430,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F3AE99-B425-4F9D-940F-AED1603DB4DA}">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -716,7 +764,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>46206.649624074067</v>
       </c>
@@ -733,7 +781,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>46206.653112071763</v>
       </c>
@@ -750,7 +798,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>46206.653112187501</v>
       </c>
@@ -767,7 +815,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>46206.65311230324</v>
       </c>
@@ -784,7 +832,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>46206.653910104164</v>
       </c>
@@ -801,7 +849,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>46206.654343599534</v>
       </c>
@@ -818,7 +866,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>46206.654343865739</v>
       </c>
@@ -835,7 +883,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>46206.654344131937</v>
       </c>
@@ -852,7 +900,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>46206.654344363429</v>
       </c>
@@ -869,7 +917,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>46206.654344641203</v>
       </c>
@@ -886,7 +934,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>46211.486990196761</v>
       </c>
@@ -903,7 +951,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>46202.667717592587</v>
       </c>
@@ -920,7 +968,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>46202.713695057872</v>
       </c>
@@ -937,7 +985,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>46205.467228125002</v>
       </c>
@@ -952,6 +1000,236 @@
       </c>
       <c r="F30" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>46198.410416666673</v>
+      </c>
+      <c r="B31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31">
+        <v>-99</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>46198.415972222218</v>
+      </c>
+      <c r="B32" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32">
+        <v>-99</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>46198.410416666673</v>
+      </c>
+      <c r="B33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33">
+        <v>-99</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>46149.473611111112</v>
+      </c>
+      <c r="B34" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34">
+        <v>-23</v>
+      </c>
+      <c r="E34" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>45883.449305555558</v>
+      </c>
+      <c r="B35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35">
+        <v>-12</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>45883.449305555558</v>
+      </c>
+      <c r="B36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36">
+        <v>-24</v>
+      </c>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>46149.473611111112</v>
+      </c>
+      <c r="B37" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37">
+        <v>-23</v>
+      </c>
+      <c r="E37" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" t="s">
+        <v>23</v>
+      </c>
+      <c r="G37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>46156.673611111109</v>
+      </c>
+      <c r="B38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38">
+        <v>-240</v>
+      </c>
+      <c r="E38" t="s">
+        <v>30</v>
+      </c>
+      <c r="F38" t="s">
+        <v>31</v>
+      </c>
+      <c r="G38" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>45931.453472222223</v>
+      </c>
+      <c r="B39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39">
+        <v>-12</v>
+      </c>
+      <c r="E39" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>45931.453472222223</v>
+      </c>
+      <c r="B40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40">
+        <v>-1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G40" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
